--- a/pacjenci/IZABELA KATYŃSKA.xlsx
+++ b/pacjenci/IZABELA KATYŃSKA.xlsx
@@ -485,7 +485,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -529,7 +529,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -573,12 +573,12 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,17 +586,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -661,7 +661,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">

--- a/pacjenci/IZABELA KATYŃSKA.xlsx
+++ b/pacjenci/IZABELA KATYŃSKA.xlsx
@@ -413,279 +413,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>26.07.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak grudkowy- FL low grade G1. Ocena  odpowiedzi po III cyklu chemioimmunoterapii.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 89 mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne metabolicznie,  pojedyncze i spakietowane węzły chłonne szyjne: -po stronie prawej grupy 2 wielkości do 13x23 mm  SUV max do 3,5; -po stronie lewej  grupy 2 wielkości do 19x11 mm SUV max do 3,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Nieaktywne metabolicznie węzły chłonne szyjne obustronnie wielkości do 12 mm. Niejednorodne cieniowanie w przeglądowym badaniu TK gruczołu tarczowego, z miernie powiększonym prawym płatem - do oceny w badniu USG. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę lewą.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie,  pojedyncze i spakietowane węzły chłonne: - pachowe prawe wielkości do 26x15 mm SUV max do 4,1; - pachowe lewe wielkości do 30x15 mm SUV max do 4,2; - międzypiersiowe lewe wielkości do 17x8 mm SUV max do 2,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza do 11mm - do kontroli w Echokardiografii. Nieaktywne metabolicznie węzły chłonne: - międzypiersiowe prawe wielkości do 9 mm;  - śródpiersiowe przednie wielkości do 12 mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywne metabolicznie nacieki w śródbrzuszu, podbrzuszu i w miednicy - obejmujące struktury naczyniowe oraz węzły chłonne okołoaortalne obustronnie od poziomu L1 do rozwidlenia, węzły chłonne przy naczyniach biodrowych wspólnych obustronnie, przy naczyniach biodrowych wewnętrznych i zewnętrznych obustronnie - o największych wymiarach poprzecznych  ok 83x35 mm wg PET [Im fuz 175]  na długości do 230 mm wg PET SUV max do 4,7. W części górnej naciek propaguje w kierunku głowy trzustki i wnęki wątroby - dokładna ocena zajętych struktur możliwa w badaniu TK/MR z kontrastem dożylnym.  Aktywne metabolicznie,  pojedyncze i spakietowane węzły chłonne: - pachwinowe prawe wielkości do 40x15x 29 mm SUV max do 3,3; - pachwinowe lewe wielkości do 10x19 mm SUV max do 3,2; - udowe lewe do 25 mm SUV max do 3,8. Niejednorodny metabolizm FDG  w powiększonej śledzionie [wymiar c-c 178mm]. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydatna miedniczka ekstrarenalna nerki prawej. W brzusznej części miednicy, pośrodkowo i po stronie prawej widoczna jest krągląca się strefa płynowa, wielkości ok. 52x47x50mm - w pierwszej kolejności torbiel wychodząca z prawych przydatków - wskazana kontrola ginekologiczna. Zmiana uciska i przemieszcza na stronę lewą pęcherz moczowy.  Układ kostny: Bardzo niejednorodny metabolizm FDG w układzie kostnym objętym badaniem SUV max do 3,4. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa-ciasna na poziomie C5/C6. Wydatny obszar sklerotycznej przebudowy struktury kostnej w trzonie lewej kości biodrowej, przy stawie krzyżowo-biodrowym. Os sacrum arcuatum. Niewielkie zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych.  Inne: Aktywne metabolicznie  nacieki w tkance podskórnej, ze zwapnieniami: - ramienia prawego wielkości do 12x8x38 mm wg PET SUV max do 4,9; - ramienia lewego wielkości do 29x10 mm wg PET na długości do 80 mm wg PET SUV max do 5,6  Miernie  pobudzone metabolicznie zmiany w tkance podskórnej podbrzusza- w pierwszej kolejności poiniekcyjne. Cechy obrzęku limfatycznego kończyn dolnych, zwłaszcza po stronie lewej.  Wartości referencyjne: MBPS SUVmax 1,4; Prawy płat wątroby SUVmax do 2,4.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie choroby chłoniakowej, z masywnym zajęciem węzłów chłonnych jamy brzusznej i miednicy oraz  węzłów chłonnych  szyi i klatki piersiowej, a także tkanki podskórnej.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>5.6</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>27.09.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak grudkowy- FL low grade G1. Ocena remmisji choroby po VI cyklach chemioimmunoterapii.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do stopy (2 metry). Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 83 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Miernie pobudzone metabolicznie, pojedyncze węzły chłonne szyjne: -po stronie prawej grupy 2 wielkości 15x20 mm  SUV max  2,0; [Im 493] -po stronie lewej  grupy 2 wielkości 16x12 mm SUV max 1,8. [Im 495] Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Nieaktywne metabolicznie węzły chłonne szyjne obustronnie wielkości do 10 mm. Niejednorodne cieniowanie w przeglądowym badaniu TK gruczołu tarczowego, z miernie powiększonym prawym płatem - do oceny w badniu USG. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę lewą.  Klatka piersiowa i śródpiersie: Aktywny i miernie pobudzone metabolicznie,  pojedyncze i spakietowane węzły chłonne: - pachowe prawe wielkości do 17x8 mm SUV max do 1,9; - pachowe lewe wielkości do 22x12 mm SUV max do 3,6; - międzypiersiowe lewe wielkości do 16x7 mm SUV max do 1,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne śródpiersiowe przednie wielkości do 12 mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie obszar w topografii pakietu węzłów chłonnych biodrowych zewnętrznych o wielkości wg PET do 24x13mm, SUV max do 3,8  [Im 335,329]. Obwodowa aktywność metaboliczna w obrębie torbieli wychodzącej z prawych przydatków wielkości ok. 52x45mm, SUV max 4,6. Zmiana uciska i przemieszcza na stronę lewą pęcherz moczowy  - do konsultacji ginelokogicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie nacieki wokół aorty ( wielkości do 84x48mm na poziomie naczyń nerkowych Im CT 442) oraz  naczyń biodrowych wspólnych i zewnętrznych obustronnie - grubości do 34mm [Im fuz 333]  Nieaktywne metabolicznie węzły chłonne: - pachwinowe prawe wielkości do 24x11 mm SUV max do 1,4; - pachwinowe lewe wielkości do 10x14 mm SUV max do 1,6; Niejednorodny metabolizm FDG  w powiększonej śledzionie [wymiar c-c 178mm]. Wydatna miedniczka ekstrarenalna nerki prawej.  Układ kostny: Bardzo niejednorodny metabolizm FDG w układzie kostnym objętym badaniem SUV max do 4,0. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa-ciasna na poziomie C5/C6. Wydatny obszar sklerotycznej przebudowy struktury kostnej w trzonie lewej kości biodrowej, przy stawie krzyżowo-biodrowym. Os sacrum arcuatum. Niewielkie zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych.  Inne: Miernie pobudzone metabolicznie zmiany w tkance podskórnej podbrzusza - w pierwszej kolejności poiniekcyjne. Cechy obrzęku limfatycznego kończyn dolnych, zwłaszcza po stronie lewej. Mierne pobudzenie metaboliczne w topografii struktur mięśniowych podudzia lewego, SUV max do 2,4- do kontroli.  Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 2,6.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>4.6</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>03.12.2021</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak grudkowy- FL low grade G1. Ocena remisji choroby po VIII cyklach chth.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do stopy (2 metry). Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 87 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywny metabolicznie obszar w szczęce po stronie prawej średnicy 8 mm wg PET SUV max 4,5 [Im fuz. 53]- okołozębowa zmiana zapalna- do kontroli stomatologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Nieaktywne metabolicznie węzły chłonne szyjne obustronnie wielkości do 10 mm. Niejednorodne cieniowanie w przeglądowym badaniu TK gruczołu tarczowego, z miernie powiększonym prawym płatem - do oceny w badniu USG. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę lewą.  Klatka piersiowa i śródpiersie: W śródpiersiu przednim zamostkowo miękkotkankowa struktura wielkości 29x12 mm SUV max 2,9- w pierwszej kolejności grasica. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne śródpiersiowe przednie wielkości do 12 mm oraz pachowe lewe wielkości do 12mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Wzmożony metabolizm w dnie żołądka SUV max 5,1- odczynowo?  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie nacieki wokół aorty ( wielkości do 65x20mm na poziomie naczyń nerkowych ) oraz  naczyń biodrowych wspólnych i zewnętrznych obustronnie - grubości do 20mm  Nieaktywne metabolicznie węzły chłonne pachwinowe prawe wielkości do 15x8 mm, pachwinowe lewe wielkości do 14x10 mm Wydatna miedniczka ekstrarenalna nerki prawej. Pęcherzyk średnicy 15mm w prawym jajniku.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem . Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa-ciasna na poziomie C5/C6. Wydatny obszar sklerotycznej przebudowy struktury kostnej w trzonie lewej kości biodrowej, przy stawie krzyżowo-biodrowym. Os sacrum arcuatum. Niewielkie zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych.  Inne: Miernie pobudzone metabolicznie zmiany w tkance podskórnej podbrzusza - w pierwszej kolejności poiniekcyjne.  Wartości referencyjne: MBPS SUVmax 1,5 Prawy płat wątroby SUVmax do 2,9.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Masy miękkotkankowe w jamie brzusznej i w miednicy do dalszej kontroli. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>5.1</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>06.11.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak grudkowy- FL low grade G1. Ocena remisji choroby.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do stopy (2 metry). Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 104 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywny metabolicznie obszar w topografii/w ścisłym przyleganiu do dolnego bieguna prawej ślinianki podżuchwowej, wielkości 16x13mm wg PET, SUV max 4,6 - zmiana w śliniance? ściśle przylegający węzeł chłonny przedziału IB?. Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym - do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Nieaktywne metabolicznie węzły chłonne szyjne obustronnie wielkości do 10 mm. Niejednorodne cieniowanie w przeglądowym badaniu TK gruczołu tarczowego, z miernie powiększonym prawym płatem, z ok. 6mm zwapnieniem. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę lewą.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne pachowe i śródpiersiowe wielkości do 10mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne pachwinowe lewe wielkości do 23x18mm, SUV max do 5,1. Odcinkowo zwiększona aktywność metaboliczna w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwiększona densyjność tkanki tłuszczowej w przeglądowym badaniu TK. Drobne węzly chłonne krezkowe. Węzły chłonne okołoaortalne wielkości do 10mm. Wydatna miedniczka ekstrarenalna nerki prawej. W topografii prawych przydatków strefa płynowa wielkości ok. 35x20mm - torbiel jajnika?   Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem - do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa-ciasna na poziomie C5/C6. Wydatny obszar sklerotycznej przebudowy struktury kostnej w trzonie lewej kości biodrowej, przy stawie krzyżowo-biodrowym. Os sacrum arcuatum. Niewielkie zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych.   Wartości referencyjne: MBPS SUVmax do 2,0 Prawy płat wątroby SUVmax do 3,4.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych w lewej pachwinie i niewykluczonych pojedynczych węzłów chłonnych na szyi (vide opis powyżej). Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>5.1</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>30.01.2024</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Chłoniak grudkowy- FL low grade G1. Ocena chemiowrażliwości przed kwalifikacją do HDT i autoSCT.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60min od podania 18F-FDG. Glikemia: 94 mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywny metabolicznie obszar wielkości 13mm wg PET, SUV max 7,5 w topografii grzbietowej części zachyłka zębodołowego lewej zatoki szczękowej z wydatnymi zgrubieniami błony śluzowej oraz w topografii przyległej kości szczękowej z widocznymi korzeniami zębowymi - zmiana okołowierzchołkowa? - do oceny stomatologicznej i kontroli po leczeniu p/zapalnym.  Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym - do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Wydatne okrężne zgrubienia błony śluzowej w lewej zatoce szczękowej. Nieaktywne metabolicznie węzły chłonne szyjne obustronnie wielkości do 10 mm. Niejednorodne cieniowanie w przeglądowym badaniu TK gruczołu tarczowego, z miernie powiększonym prawym płatem, z ok. 6mm zwapnieniem. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę lewą.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielka ilość płynu w worku osierdziowym zwłaszcza od strony PP i PK o szerokości płaszcza do 9mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Miernie pobudzony metabolicznie węzeł chłonny pachwinowy lewy wielkości 8mm, SUV max do 2,9 oraz udowy lewy wielkości 12mm, SUV max 2,4. Odcinkowo zwiększona aktywność metaboliczna w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydatna miedniczka ekstrarenalna nerki prawej.  Układ kostny: Zwiększony metabolizm FDG w układzie kostnym objętym badaniem - związany z prowadzonym leczeniem? Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa-ciasna na poziomie C5/C6. Drobna retrolisteza na poziomie L5/S1. Os sacrum arcuatum.  Wydatny obszar sklerotycznej przebudowy struktury kostnej w trzonie lewej kości biodrowej, przy stawie krzyżowo-biodrowym. Niewielkie zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 3,0.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie obszar w topografii grzbietowej części zachyłka zębodołowego lewej zatoki szczękowej z wydatnymi zgrubieniami błony śluzowej oraz w topografii przyległej kości szczękowej z widocznymi korzeniami zębowymi - zmiana okołowierzchołkowa? - do oceny stomatologicznej i kontroli po leczeniu p/zapalnym/ oceny z całością obrazu klinicznego. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>7.5</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/IZABELA KATYŃSKA.xlsx
+++ b/pacjenci/IZABELA KATYŃSKA.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 89 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie,  pojedyncze i spakietowane węzły chłonne szyjne: -po stronie prawej grupy 2 wielkości do 13x23 mm  SUV max do 3,5; -po stronie lewej  grupy 2 wielkości do 19x11 mm SUV max do 3,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Nieaktywne metabolicznie węzły chłonne szyjne obustronnie wielkości do 12 mm. Niejednorodne cieniowanie w przeglądowym badaniu TK gruczołu tarczowego, z miernie powiększonym prawym płatem - do oceny w badniu USG. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę lewą.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie,  pojedyncze i spakietowane węzły chłonne: - pachowe prawe wielkości do 26x15 mm SUV max do 4,1; - pachowe lewe wielkości do 30x15 mm SUV max do 4,2; - międzypiersiowe lewe wielkości do 17x8 mm SUV max do 2,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza do 11mm - do kontroli w Echokardiografii. Nieaktywne metabolicznie węzły chłonne: - międzypiersiowe prawe wielkości do 9 mm;  - śródpiersiowe przednie wielkości do 12 mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywne metabolicznie nacieki w śródbrzuszu, podbrzuszu i w miednicy - obejmujące struktury naczyniowe oraz węzły chłonne okołoaortalne obustronnie od poziomu L1 do rozwidlenia, węzły chłonne przy naczyniach biodrowych wspólnych obustronnie, przy naczyniach biodrowych wewnętrznych i zewnętrznych obustronnie - o największych wymiarach poprzecznych  ok 83x35 mm wg PET [Im fuz 175]  na długości do 230 mm wg PET SUV max do 4,7. W części górnej naciek propaguje w kierunku głowy trzustki i wnęki wątroby - dokładna ocena zajętych struktur możliwa w badaniu TK/MR z kontrastem dożylnym.  Aktywne metabolicznie,  pojedyncze i spakietowane węzły chłonne: - pachwinowe prawe wielkości do 40x15x 29 mm SUV max do 3,3; - pachwinowe lewe wielkości do 10x19 mm SUV max do 3,2; - udowe lewe do 25 mm SUV max do 3,8. Niejednorodny metabolizm FDG  w powiększonej śledzionie [wymiar c-c 178mm]. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydatna miedniczka ekstrarenalna nerki prawej. W brzusznej części miednicy, pośrodkowo i po stronie prawej widoczna jest krągląca się strefa płynowa, wielkości ok. 52x47x50mm - w pierwszej kolejności torbiel wychodząca z prawych przydatków - wskazana kontrola ginekologiczna. Zmiana uciska i przemieszcza na stronę lewą pęcherz moczowy.  Układ kostny: Bardzo niejednorodny metabolizm FDG w układzie kostnym objętym badaniem SUV max do 3,4. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa-ciasna na poziomie C5/C6. Wydatny obszar sklerotycznej przebudowy struktury kostnej w trzonie lewej kości biodrowej, przy stawie krzyżowo-biodrowym. Os sacrum arcuatum. Niewielkie zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych.  Inne: Aktywne metabolicznie  nacieki w tkance podskórnej, ze zwapnieniami: - ramienia prawego wielkości do 12x8x38 mm wg PET SUV max do 4,9; - ramienia lewego wielkości do 29x10 mm wg PET na długości do 80 mm wg PET SUV max do 5,6  Miernie  pobudzone metabolicznie zmiany w tkance podskórnej podbrzusza- w pierwszej kolejności poiniekcyjne. Cechy obrzęku limfatycznego kończyn dolnych, zwłaszcza po stronie lewej.  Wartości referencyjne: MBPS SUVmax 1,4; Prawy płat wątroby SUVmax do 2,4.</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie,  pojedyncze i spakietowane węzły chłonne szyjne: -po stronie prawej grupy 2 wielkości do 13x23 mm  SUV max do 3,5; -po stronie lewej  grupy 2 wielkości do 19x11 mm SUV max do 3,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Nieaktywne metabolicznie węzły chłonne szyjne obustronnie wielkości do 12 mm. Niejednorodne cieniowanie w przeglądowym badaniu TK gruczołu tarczowego, z miernie powiększonym prawym płatem - do oceny w badniu USG. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę lewą.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie,  pojedyncze i spakietowane węzły chłonne: - pachowe prawe wielkości do 26x15 mm SUV max do 4,1; - pachowe lewe wielkości do 30x15 mm SUV max do 4,2; - międzypiersiowe lewe wielkości do 17x8 mm SUV max do 2,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza do 11mm - do kontroli w Echokardiografii. Nieaktywne metabolicznie węzły chłonne: - międzypiersiowe prawe wielkości do 9 mm;  - śródpiersiowe przednie wielkości do 12 mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie nacieki w śródbrzuszu, podbrzuszu i w miednicy - obejmujące struktury naczyniowe oraz węzły chłonne okołoaortalne obustronnie od poziomu L1 do rozwidlenia, węzły chłonne przy naczyniach biodrowych wspólnych obustronnie, przy naczyniach biodrowych wewnętrznych i zewnętrznych obustronnie - o największych wymiarach poprzecznych  ok 83x35 mm wg PET [Im fuz 175]  na długości do 230 mm wg PET SUV max do 4,7. W części górnej naciek propaguje w kierunku głowy trzustki i wnęki wątroby - dokładna ocena zajętych struktur możliwa w badaniu TK/MR z kontrastem dożylnym.  Aktywne metabolicznie,  pojedyncze i spakietowane węzły chłonne: - pachwinowe prawe wielkości do 40x15x 29 mm SUV max do 3,3; - pachwinowe lewe wielkości do 10x19 mm SUV max do 3,2; - udowe lewe do 25 mm SUV max do 3,8. Niejednorodny metabolizm FDG  w powiększonej śledzionie [wymiar c-c 178mm]. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydatna miedniczka ekstrarenalna nerki prawej. W brzusznej części miednicy, pośrodkowo i po stronie prawej widoczna jest krągląca się strefa płynowa, wielkości ok. 52x47x50mm - w pierwszej kolejności torbiel wychodząca z prawych przydatków - wskazana kontrola ginekologiczna. Zmiana uciska i przemieszcza na stronę lewą pęcherz moczowy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Bardzo niejednorodny metabolizm FDG w układzie kostnym objętym badaniem SUV max do 3,4. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa-ciasna na poziomie C5/C6. Wydatny obszar sklerotycznej przebudowy struktury kostnej w trzonie lewej kości biodrowej, przy stawie krzyżowo-biodrowym. Os sacrum arcuatum. Niewielkie zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych.  Inne: Aktywne metabolicznie  nacieki w tkance podskórnej, ze zwapnieniami: - ramienia prawego wielkości do 12x8x38 mm wg PET SUV max do 4,9; - ramienia lewego wielkości do 29x10 mm wg PET na długości do 80 mm wg PET SUV max do 5,6  Miernie  pobudzone metabolicznie zmiany w tkance podskórnej podbrzusza- w pierwszej kolejności poiniekcyjne. Cechy obrzęku limfatycznego kończyn dolnych, zwłaszcza po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie choroby chłoniakowej, z masywnym zajęciem węzłów chłonnych jamy brzusznej i miednicy oraz  węzłów chłonnych  szyi i klatki piersiowej, a także tkanki podskórnej.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>5.6</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do stopy (2 metry). Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 83 mg%.</t>
+          <t>od szczytu głowy do stopy (2 metry).</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Miernie pobudzone metabolicznie, pojedyncze węzły chłonne szyjne: -po stronie prawej grupy 2 wielkości 15x20 mm  SUV max  2,0; [Im 493] -po stronie lewej  grupy 2 wielkości 16x12 mm SUV max 1,8. [Im 495] Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Nieaktywne metabolicznie węzły chłonne szyjne obustronnie wielkości do 10 mm. Niejednorodne cieniowanie w przeglądowym badaniu TK gruczołu tarczowego, z miernie powiększonym prawym płatem - do oceny w badniu USG. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę lewą.  Klatka piersiowa i śródpiersie: Aktywny i miernie pobudzone metabolicznie,  pojedyncze i spakietowane węzły chłonne: - pachowe prawe wielkości do 17x8 mm SUV max do 1,9; - pachowe lewe wielkości do 22x12 mm SUV max do 3,6; - międzypiersiowe lewe wielkości do 16x7 mm SUV max do 1,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne śródpiersiowe przednie wielkości do 12 mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie obszar w topografii pakietu węzłów chłonnych biodrowych zewnętrznych o wielkości wg PET do 24x13mm, SUV max do 3,8  [Im 335,329]. Obwodowa aktywność metaboliczna w obrębie torbieli wychodzącej z prawych przydatków wielkości ok. 52x45mm, SUV max 4,6. Zmiana uciska i przemieszcza na stronę lewą pęcherz moczowy  - do konsultacji ginelokogicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie nacieki wokół aorty ( wielkości do 84x48mm na poziomie naczyń nerkowych Im CT 442) oraz  naczyń biodrowych wspólnych i zewnętrznych obustronnie - grubości do 34mm [Im fuz 333]  Nieaktywne metabolicznie węzły chłonne: - pachwinowe prawe wielkości do 24x11 mm SUV max do 1,4; - pachwinowe lewe wielkości do 10x14 mm SUV max do 1,6; Niejednorodny metabolizm FDG  w powiększonej śledzionie [wymiar c-c 178mm]. Wydatna miedniczka ekstrarenalna nerki prawej.  Układ kostny: Bardzo niejednorodny metabolizm FDG w układzie kostnym objętym badaniem SUV max do 4,0. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa-ciasna na poziomie C5/C6. Wydatny obszar sklerotycznej przebudowy struktury kostnej w trzonie lewej kości biodrowej, przy stawie krzyżowo-biodrowym. Os sacrum arcuatum. Niewielkie zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych.  Inne: Miernie pobudzone metabolicznie zmiany w tkance podskórnej podbrzusza - w pierwszej kolejności poiniekcyjne. Cechy obrzęku limfatycznego kończyn dolnych, zwłaszcza po stronie lewej. Mierne pobudzenie metaboliczne w topografii struktur mięśniowych podudzia lewego, SUV max do 2,4- do kontroli.  Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 2,6.</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Miernie pobudzone metabolicznie, pojedyncze węzły chłonne szyjne: -po stronie prawej grupy 2 wielkości 15x20 mm  SUV max  2,0; [Im 493] -po stronie lewej  grupy 2 wielkości 16x12 mm SUV max 1,8. [Im 495] Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Nieaktywne metabolicznie węzły chłonne szyjne obustronnie wielkości do 10 mm. Niejednorodne cieniowanie w przeglądowym badaniu TK gruczołu tarczowego, z miernie powiększonym prawym płatem - do oceny w badniu USG. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę lewą.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Aktywny i miernie pobudzone metabolicznie,  pojedyncze i spakietowane węzły chłonne: - pachowe prawe wielkości do 17x8 mm SUV max do 1,9; - pachowe lewe wielkości do 22x12 mm SUV max do 3,6; - międzypiersiowe lewe wielkości do 16x7 mm SUV max do 1,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne śródpiersiowe przednie wielkości do 12 mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w topografii pakietu węzłów chłonnych biodrowych zewnętrznych o wielkości wg PET do 24x13mm, SUV max do 3,8  [Im 335,329]. Obwodowa aktywność metaboliczna w obrębie torbieli wychodzącej z prawych przydatków wielkości ok. 52x45mm, SUV max 4,6. Zmiana uciska i przemieszcza na stronę lewą pęcherz moczowy  - do konsultacji ginelokogicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie nacieki wokół aorty ( wielkości do 84x48mm na poziomie naczyń nerkowych Im CT 442) oraz  naczyń biodrowych wspólnych i zewnętrznych obustronnie - grubości do 34mm [Im fuz 333]  Nieaktywne metabolicznie węzły chłonne: - pachwinowe prawe wielkości do 24x11 mm SUV max do 1,4; - pachwinowe lewe wielkości do 10x14 mm SUV max do 1,6; Niejednorodny metabolizm FDG  w powiększonej śledzionie [wymiar c-c 178mm]. Wydatna miedniczka ekstrarenalna nerki prawej.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Bardzo niejednorodny metabolizm FDG w układzie kostnym objętym badaniem SUV max do 4,0. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa-ciasna na poziomie C5/C6. Wydatny obszar sklerotycznej przebudowy struktury kostnej w trzonie lewej kości biodrowej, przy stawie krzyżowo-biodrowym. Os sacrum arcuatum. Niewielkie zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych.  Inne: Miernie pobudzone metabolicznie zmiany w tkance podskórnej podbrzusza - w pierwszej kolejności poiniekcyjne. Cechy obrzęku limfatycznego kończyn dolnych, zwłaszcza po stronie lewej. Mierne pobudzenie metaboliczne w topografii struktur mięśniowych podudzia lewego, SUV max do 2,4- do kontroli.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>4.6</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do stopy (2 metry). Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 87 mg%.</t>
+          <t>od szczytu głowy do stopy (2 metry).</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Aktywny metabolicznie obszar w szczęce po stronie prawej średnicy 8 mm wg PET SUV max 4,5 [Im fuz. 53]- okołozębowa zmiana zapalna- do kontroli stomatologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Nieaktywne metabolicznie węzły chłonne szyjne obustronnie wielkości do 10 mm. Niejednorodne cieniowanie w przeglądowym badaniu TK gruczołu tarczowego, z miernie powiększonym prawym płatem - do oceny w badniu USG. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę lewą.  Klatka piersiowa i śródpiersie: W śródpiersiu przednim zamostkowo miękkotkankowa struktura wielkości 29x12 mm SUV max 2,9- w pierwszej kolejności grasica. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne śródpiersiowe przednie wielkości do 12 mm oraz pachowe lewe wielkości do 12mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Wzmożony metabolizm w dnie żołądka SUV max 5,1- odczynowo?  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie nacieki wokół aorty ( wielkości do 65x20mm na poziomie naczyń nerkowych ) oraz  naczyń biodrowych wspólnych i zewnętrznych obustronnie - grubości do 20mm  Nieaktywne metabolicznie węzły chłonne pachwinowe prawe wielkości do 15x8 mm, pachwinowe lewe wielkości do 14x10 mm Wydatna miedniczka ekstrarenalna nerki prawej. Pęcherzyk średnicy 15mm w prawym jajniku.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem . Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa-ciasna na poziomie C5/C6. Wydatny obszar sklerotycznej przebudowy struktury kostnej w trzonie lewej kości biodrowej, przy stawie krzyżowo-biodrowym. Os sacrum arcuatum. Niewielkie zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych.  Inne: Miernie pobudzone metabolicznie zmiany w tkance podskórnej podbrzusza - w pierwszej kolejności poiniekcyjne.  Wartości referencyjne: MBPS SUVmax 1,5 Prawy płat wątroby SUVmax do 2,9.</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w szczęce po stronie prawej średnicy 8 mm wg PET SUV max 4,5 [Im fuz. 53]- okołozębowa zmiana zapalna- do kontroli stomatologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Nieaktywne metabolicznie węzły chłonne szyjne obustronnie wielkości do 10 mm. Niejednorodne cieniowanie w przeglądowym badaniu TK gruczołu tarczowego, z miernie powiększonym prawym płatem - do oceny w badniu USG. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę lewą.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>W śródpiersiu przednim zamostkowo miękkotkankowa struktura wielkości 29x12 mm SUV max 2,9- w pierwszej kolejności grasica. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne śródpiersiowe przednie wielkości do 12 mm oraz pachowe lewe wielkości do 12mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm w dnie żołądka SUV max 5,1- odczynowo?  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie nacieki wokół aorty ( wielkości do 65x20mm na poziomie naczyń nerkowych ) oraz  naczyń biodrowych wspólnych i zewnętrznych obustronnie - grubości do 20mm  Nieaktywne metabolicznie węzły chłonne pachwinowe prawe wielkości do 15x8 mm, pachwinowe lewe wielkości do 14x10 mm Wydatna miedniczka ekstrarenalna nerki prawej. Pęcherzyk średnicy 15mm w prawym jajniku.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem . Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa-ciasna na poziomie C5/C6. Wydatny obszar sklerotycznej przebudowy struktury kostnej w trzonie lewej kości biodrowej, przy stawie krzyżowo-biodrowym. Os sacrum arcuatum. Niewielkie zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych.  Inne: Miernie pobudzone metabolicznie zmiany w tkance podskórnej podbrzusza - w pierwszej kolejności poiniekcyjne.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Masy miękkotkankowe w jamie brzusznej i w miednicy do dalszej kontroli. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>5.1</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do stopy (2 metry). Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 104 mg%.</t>
+          <t>od szczytu głowy do stopy (2 metry).</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Aktywny metabolicznie obszar w topografii/w ścisłym przyleganiu do dolnego bieguna prawej ślinianki podżuchwowej, wielkości 16x13mm wg PET, SUV max 4,6 - zmiana w śliniance? ściśle przylegający węzeł chłonny przedziału IB?. Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym - do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Nieaktywne metabolicznie węzły chłonne szyjne obustronnie wielkości do 10 mm. Niejednorodne cieniowanie w przeglądowym badaniu TK gruczołu tarczowego, z miernie powiększonym prawym płatem, z ok. 6mm zwapnieniem. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę lewą.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne pachowe i śródpiersiowe wielkości do 10mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne pachwinowe lewe wielkości do 23x18mm, SUV max do 5,1. Odcinkowo zwiększona aktywność metaboliczna w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwiększona densyjność tkanki tłuszczowej w przeglądowym badaniu TK. Drobne węzly chłonne krezkowe. Węzły chłonne okołoaortalne wielkości do 10mm. Wydatna miedniczka ekstrarenalna nerki prawej. W topografii prawych przydatków strefa płynowa wielkości ok. 35x20mm - torbiel jajnika?   Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem - do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa-ciasna na poziomie C5/C6. Wydatny obszar sklerotycznej przebudowy struktury kostnej w trzonie lewej kości biodrowej, przy stawie krzyżowo-biodrowym. Os sacrum arcuatum. Niewielkie zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych.   Wartości referencyjne: MBPS SUVmax do 2,0 Prawy płat wątroby SUVmax do 3,4.</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w topografii/w ścisłym przyleganiu do dolnego bieguna prawej ślinianki podżuchwowej, wielkości 16x13mm wg PET, SUV max 4,6 - zmiana w śliniance? ściśle przylegający węzeł chłonny przedziału IB?. Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym - do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Nieaktywne metabolicznie węzły chłonne szyjne obustronnie wielkości do 10 mm. Niejednorodne cieniowanie w przeglądowym badaniu TK gruczołu tarczowego, z miernie powiększonym prawym płatem, z ok. 6mm zwapnieniem. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę lewą.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne pachowe i śródpiersiowe wielkości do 10mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne pachwinowe lewe wielkości do 23x18mm, SUV max do 5,1. Odcinkowo zwiększona aktywność metaboliczna w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwiększona densyjność tkanki tłuszczowej w przeglądowym badaniu TK. Drobne węzly chłonne krezkowe. Węzły chłonne okołoaortalne wielkości do 10mm. Wydatna miedniczka ekstrarenalna nerki prawej. W topografii prawych przydatków strefa płynowa wielkości ok. 35x20mm - torbiel jajnika?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem - do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa-ciasna na poziomie C5/C6. Wydatny obszar sklerotycznej przebudowy struktury kostnej w trzonie lewej kości biodrowej, przy stawie krzyżowo-biodrowym. Os sacrum arcuatum. Niewielkie zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych w lewej pachwinie i niewykluczonych pojedynczych węzłów chłonnych na szyi (vide opis powyżej). Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>5.1</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60min od podania 18F-FDG. Glikemia: 94 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Aktywny metabolicznie obszar wielkości 13mm wg PET, SUV max 7,5 w topografii grzbietowej części zachyłka zębodołowego lewej zatoki szczękowej z wydatnymi zgrubieniami błony śluzowej oraz w topografii przyległej kości szczękowej z widocznymi korzeniami zębowymi - zmiana okołowierzchołkowa? - do oceny stomatologicznej i kontroli po leczeniu p/zapalnym.  Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym - do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Wydatne okrężne zgrubienia błony śluzowej w lewej zatoce szczękowej. Nieaktywne metabolicznie węzły chłonne szyjne obustronnie wielkości do 10 mm. Niejednorodne cieniowanie w przeglądowym badaniu TK gruczołu tarczowego, z miernie powiększonym prawym płatem, z ok. 6mm zwapnieniem. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę lewą.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielka ilość płynu w worku osierdziowym zwłaszcza od strony PP i PK o szerokości płaszcza do 9mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Miernie pobudzony metabolicznie węzeł chłonny pachwinowy lewy wielkości 8mm, SUV max do 2,9 oraz udowy lewy wielkości 12mm, SUV max 2,4. Odcinkowo zwiększona aktywność metaboliczna w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydatna miedniczka ekstrarenalna nerki prawej.  Układ kostny: Zwiększony metabolizm FDG w układzie kostnym objętym badaniem - związany z prowadzonym leczeniem? Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa-ciasna na poziomie C5/C6. Drobna retrolisteza na poziomie L5/S1. Os sacrum arcuatum.  Wydatny obszar sklerotycznej przebudowy struktury kostnej w trzonie lewej kości biodrowej, przy stawie krzyżowo-biodrowym. Niewielkie zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 3,0.</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar wielkości 13mm wg PET, SUV max 7,5 w topografii grzbietowej części zachyłka zębodołowego lewej zatoki szczękowej z wydatnymi zgrubieniami błony śluzowej oraz w topografii przyległej kości szczękowej z widocznymi korzeniami zębowymi - zmiana okołowierzchołkowa? - do oceny stomatologicznej i kontroli po leczeniu p/zapalnym.  Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym - do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Wydatne okrężne zgrubienia błony śluzowej w lewej zatoce szczękowej. Nieaktywne metabolicznie węzły chłonne szyjne obustronnie wielkości do 10 mm. Niejednorodne cieniowanie w przeglądowym badaniu TK gruczołu tarczowego, z miernie powiększonym prawym płatem, z ok. 6mm zwapnieniem. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę lewą.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielka ilość płynu w worku osierdziowym zwłaszcza od strony PP i PK o szerokości płaszcza do 9mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Miernie pobudzony metabolicznie węzeł chłonny pachwinowy lewy wielkości 8mm, SUV max do 2,9 oraz udowy lewy wielkości 12mm, SUV max 2,4. Odcinkowo zwiększona aktywność metaboliczna w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydatna miedniczka ekstrarenalna nerki prawej.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Zwiększony metabolizm FDG w układzie kostnym objętym badaniem - związany z prowadzonym leczeniem? Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa-ciasna na poziomie C5/C6. Drobna retrolisteza na poziomie L5/S1. Os sacrum arcuatum.  Wydatny obszar sklerotycznej przebudowy struktury kostnej w trzonie lewej kości biodrowej, przy stawie krzyżowo-biodrowym. Niewielkie zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie obszar w topografii grzbietowej części zachyłka zębodołowego lewej zatoki szczękowej z wydatnymi zgrubieniami błony śluzowej oraz w topografii przyległej kości szczękowej z widocznymi korzeniami zębowymi - zmiana okołowierzchołkowa? - do oceny stomatologicznej i kontroli po leczeniu p/zapalnym/ oceny z całością obrazu klinicznego. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>7.5</v>
       </c>
     </row>
